--- a/域名映射.xlsx
+++ b/域名映射.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>项目</t>
   </si>
@@ -90,6 +90,42 @@
   </si>
   <si>
     <t>wesar.cn</t>
+  </si>
+  <si>
+    <t>www.topfirefighting.com</t>
+  </si>
+  <si>
+    <t>topfirefighting.com</t>
+  </si>
+  <si>
+    <t>www.bottlecapmeta.com</t>
+  </si>
+  <si>
+    <t>bottlecapmeta.com</t>
+  </si>
+  <si>
+    <t>www.toumeipro.com</t>
+  </si>
+  <si>
+    <t>toumeipro.com</t>
+  </si>
+  <si>
+    <t>www.cnvicast.com</t>
+  </si>
+  <si>
+    <t>cnvicast.com</t>
+  </si>
+  <si>
+    <t>www.againvape.com</t>
+  </si>
+  <si>
+    <t>againvape.com</t>
+  </si>
+  <si>
+    <t>www.trodatcn.com</t>
+  </si>
+  <si>
+    <t>trodatcn.com</t>
   </si>
 </sst>
 </file>
@@ -711,7 +747,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -719,6 +755,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1032,7 +1071,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="30.375" customWidth="1"/>
@@ -1148,26 +1187,71 @@
       <c r="D11" s="2"/>
     </row>
     <row r="12" ht="18.75" spans="1:4">
-      <c r="B12" s="1"/>
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
     <row r="13" ht="18.75" spans="1:4">
-      <c r="B13" s="1"/>
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
     <row r="14" ht="18.75" spans="1:4">
-      <c r="B14" s="1"/>
+      <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
     <row r="15" ht="18.75" spans="1:4">
-      <c r="B15" s="1"/>
+      <c r="A15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A14" r:id="rId1" display="www.toumeipro.com"/>
+    <hyperlink ref="A15" r:id="rId2" display="www.cnvicast.com"/>
+    <hyperlink ref="A16" r:id="rId3" display="www.againvape.com"/>
+    <hyperlink ref="A17" r:id="rId4" display="www.trodatcn.com" tooltip="http://www.trodatcn.com"/>
+    <hyperlink ref="B15" r:id="rId2" display="cnvicast.com"/>
+    <hyperlink ref="B16" r:id="rId3" display="againvape.com"/>
+    <hyperlink ref="B17" r:id="rId4" display="trodatcn.com" tooltip="http://www.trodatcn.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
